--- a/files/港岛-香港仔及鸭脷洲-PORTO.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-PORTO.xlsx
@@ -271,10 +271,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6358,7 +6358,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7552,7 +7552,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7800,7 +7800,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8172,7 +8172,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8730,7 +8730,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9412,7 +9412,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9660,7 +9660,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9722,7 +9722,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9779,34 +9779,34 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
-        <v>7525000</v>
+        <v>6225000</v>
       </c>
       <c r="I145" s="5" t="n">
-        <v>27264</v>
+        <v>22554</v>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K145" s="5" t="n">
-        <v>6283375</v>
+        <v>6225000</v>
       </c>
       <c r="L145" s="5" t="n">
-        <v>22766</v>
+        <v>22554</v>
       </c>
       <c r="M145" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N145" s="3" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -10218,7 +10218,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10280,7 +10280,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10342,7 +10342,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10528,7 +10528,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10776,7 +10776,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10962,7 +10962,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -11886,7 +11886,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>65</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -11965,12 +11965,49 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
+          <t>28&amp;29</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 746呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 644呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+      <c r="H5" s="21" t="inlineStr"/>
+      <c r="I5" s="21" t="inlineStr"/>
+      <c r="J5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="20" t="inlineStr"/>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 286呎 (1房)
 -
@@ -11978,49 +12015,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr"/>
-      <c r="F5" s="20" t="inlineStr"/>
-      <c r="G5" s="20" t="inlineStr"/>
-      <c r="H5" s="20" t="inlineStr"/>
-      <c r="I5" s="20" t="inlineStr"/>
-      <c r="J5" s="20" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>28&amp;29</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>B | 746呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr">
-        <is>
-          <t>D | 644呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+      <c r="I6" s="21" t="inlineStr"/>
+      <c r="J6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -12028,7 +12028,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 388呎 (2房)
 -
@@ -12044,7 +12044,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12068,7 +12068,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12076,7 +12076,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12084,8 +12084,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr"/>
-      <c r="J7" s="20" t="inlineStr"/>
+      <c r="I7" s="21" t="inlineStr"/>
+      <c r="J7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -12093,7 +12093,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 388呎 (2房)
 -
@@ -12109,7 +12109,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12133,7 +12133,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12141,7 +12141,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12149,8 +12149,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I8" s="20" t="inlineStr"/>
-      <c r="J8" s="20" t="inlineStr"/>
+      <c r="I8" s="21" t="inlineStr"/>
+      <c r="J8" s="21" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -12174,7 +12174,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12198,7 +12198,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12206,7 +12206,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12214,8 +12214,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I9" s="20" t="inlineStr"/>
-      <c r="J9" s="20" t="inlineStr"/>
+      <c r="I9" s="21" t="inlineStr"/>
+      <c r="J9" s="21" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -12236,7 +12236,7 @@
           <t>B | 241呎 (1房)
 $720万
 $29,871/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -12263,7 +12263,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12271,7 +12271,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H10" s="21" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12279,8 +12279,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I10" s="20" t="inlineStr"/>
-      <c r="J10" s="20" t="inlineStr"/>
+      <c r="I10" s="21" t="inlineStr"/>
+      <c r="J10" s="21" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -12328,7 +12328,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12336,7 +12336,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H11" s="21" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12344,8 +12344,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I11" s="20" t="inlineStr"/>
-      <c r="J11" s="20" t="inlineStr"/>
+      <c r="I11" s="21" t="inlineStr"/>
+      <c r="J11" s="21" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -12393,7 +12393,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12401,7 +12401,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12409,8 +12409,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I12" s="20" t="inlineStr"/>
-      <c r="J12" s="20" t="inlineStr"/>
+      <c r="I12" s="21" t="inlineStr"/>
+      <c r="J12" s="21" t="inlineStr"/>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -12431,7 +12431,7 @@
           <t>B | 241呎 (1房)
 $693万
 $28,743/呎
-(26年-06月-23日)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -12466,7 +12466,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H13" s="21" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12474,8 +12474,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I13" s="20" t="inlineStr"/>
-      <c r="J13" s="20" t="inlineStr"/>
+      <c r="I13" s="21" t="inlineStr"/>
+      <c r="J13" s="21" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -12488,7 +12488,7 @@
           <t>A | 388呎 (2房)
 $1037万
 $26,727/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -12520,7 +12520,7 @@
           <t>E | 255呎 (1房)
 $648万
 $25,412/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -12531,7 +12531,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H14" s="21" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12539,8 +12539,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I14" s="20" t="inlineStr"/>
-      <c r="J14" s="20" t="inlineStr"/>
+      <c r="I14" s="21" t="inlineStr"/>
+      <c r="J14" s="21" t="inlineStr"/>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -12561,7 +12561,7 @@
           <t>B | 241呎 (1房)
 $675万
 $27,996/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -12585,7 +12585,7 @@
           <t>E | 255呎 (1房)
 $626万
 $24,549/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -12604,8 +12604,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I15" s="20" t="inlineStr"/>
-      <c r="J15" s="20" t="inlineStr"/>
+      <c r="I15" s="21" t="inlineStr"/>
+      <c r="J15" s="21" t="inlineStr"/>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -12618,7 +12618,7 @@
           <t>A | 388呎 (2房)
 $970万
 $25,000/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
@@ -12626,7 +12626,7 @@
           <t>B | 241呎 (1房)
 $653万
 $27,108/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
@@ -12634,7 +12634,7 @@
           <t>C | 436呎 (2房)
 $1155万
 $26,495/呎
-(26年-07月-15日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="E16" s="24" t="inlineStr">
@@ -12642,7 +12642,7 @@
           <t>D | 270呎 (1房)
 $676万
 $25,026/呎
-(26年-07月-13日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="F16" s="24" t="inlineStr">
@@ -12650,7 +12650,7 @@
           <t>E | 255呎 (1房)
 $621万
 $24,349/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="G16" s="23" t="inlineStr">
@@ -12669,8 +12669,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I16" s="20" t="inlineStr"/>
-      <c r="J16" s="20" t="inlineStr"/>
+      <c r="I16" s="21" t="inlineStr"/>
+      <c r="J16" s="21" t="inlineStr"/>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -12683,7 +12683,7 @@
           <t>A | 388呎 (2房)
 $954万
 $24,601/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
@@ -12691,7 +12691,7 @@
           <t>B | 241呎 (1房)
 $652万
 $27,037/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr">
@@ -12699,7 +12699,7 @@
           <t>C | 436呎 (2房)
 $1085万
 $24,894/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="E17" s="24" t="inlineStr">
@@ -12707,7 +12707,7 @@
           <t>D | 270呎 (1房)
 $641万
 $23,733/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="F17" s="24" t="inlineStr">
@@ -12715,7 +12715,7 @@
           <t>E | 255呎 (1房)
 $610万
 $23,922/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -12734,8 +12734,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I17" s="20" t="inlineStr"/>
-      <c r="J17" s="20" t="inlineStr"/>
+      <c r="I17" s="21" t="inlineStr"/>
+      <c r="J17" s="21" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -12748,7 +12748,7 @@
           <t>A | 388呎 (2房)
 $974万
 $25,103/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -12756,7 +12756,7 @@
           <t>B | 241呎 (1房)
 $638万
 $26,490/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -12780,7 +12780,7 @@
           <t>E | 255呎 (1房)
 $611万
 $23,949/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -12799,8 +12799,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I18" s="20" t="inlineStr"/>
-      <c r="J18" s="20" t="inlineStr"/>
+      <c r="I18" s="21" t="inlineStr"/>
+      <c r="J18" s="21" t="inlineStr"/>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
@@ -12813,7 +12813,7 @@
           <t>A | 388呎 (2房)
 $904万
 $23,299/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -12821,7 +12821,7 @@
           <t>B | 241呎 (1房)
 $628万
 $26,071/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="D19" s="24" t="inlineStr">
@@ -12829,7 +12829,7 @@
           <t>C | 436呎 (2房)
 $1016万
 $23,300/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -12845,7 +12845,7 @@
           <t>E | 255呎 (1房)
 $606万
 $23,749/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="G19" s="23" t="inlineStr">
@@ -12864,8 +12864,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I19" s="20" t="inlineStr"/>
-      <c r="J19" s="20" t="inlineStr"/>
+      <c r="I19" s="21" t="inlineStr"/>
+      <c r="J19" s="21" t="inlineStr"/>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
@@ -12886,7 +12886,7 @@
           <t>B | 241呎 (1房)
 $605万
 $25,100/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
@@ -12894,7 +12894,7 @@
           <t>C | 436呎 (2房)
 $1038万
 $23,819/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
@@ -12905,7 +12905,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 296呎 (1房)
 -
@@ -12913,7 +12913,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G20" s="21" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 346呎 (2房)
 -
@@ -12929,8 +12929,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I20" s="20" t="inlineStr"/>
-      <c r="J20" s="20" t="inlineStr"/>
+      <c r="I20" s="21" t="inlineStr"/>
+      <c r="J20" s="21" t="inlineStr"/>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
@@ -12943,7 +12943,7 @@
           <t>A | 389呎 (2房)
 $922万
 $23,715/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
@@ -12951,7 +12951,7 @@
           <t>B | 241呎 (1房)
 $598万
 $24,801/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
@@ -12975,7 +12975,7 @@
           <t>E | 276呎 (1房)
 $639万
 $23,149/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="G21" s="24" t="inlineStr">
@@ -12983,7 +12983,7 @@
           <t>F | 288呎 (1房)
 $687万
 $23,868/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="H21" s="24" t="inlineStr">
@@ -12991,7 +12991,7 @@
           <t>G | 277呎 (1房)
 $661万
 $23,870/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="I21" s="23" t="inlineStr">
@@ -13022,7 +13022,7 @@
           <t>A | 389呎 (2房)
 $889万
 $22,851/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -13030,7 +13030,7 @@
           <t>B | 241呎 (1房)
 $585万
 $24,261/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="D22" s="24" t="inlineStr">
@@ -13038,7 +13038,7 @@
           <t>C | 438呎 (2房)
 $994万
 $22,701/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="E22" s="24" t="inlineStr">
@@ -13046,7 +13046,7 @@
           <t>D | 271呎 (1房)
 $616万
 $22,742/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="F22" s="24" t="inlineStr">
@@ -13054,7 +13054,7 @@
           <t>E | 276呎 (1房)
 $631万
 $22,851/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="G22" s="24" t="inlineStr">
@@ -13062,7 +13062,7 @@
           <t>F | 288呎 (1房)
 $654万
 $22,698/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="H22" s="24" t="inlineStr">
@@ -13070,7 +13070,7 @@
           <t>G | 277呎 (1房)
 $633万
 $22,848/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="I22" s="23" t="inlineStr">
@@ -13101,7 +13101,7 @@
           <t>A | 389呎 (2房)
 $881万
 $22,650/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -13109,7 +13109,7 @@
           <t>B | 241呎 (1房)
 $583万
 $24,199/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -13125,7 +13125,7 @@
           <t>D | 271呎 (1房)
 $604万
 $22,299/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="F23" s="24" t="inlineStr">
@@ -13133,7 +13133,7 @@
           <t>E | 276呎 (1房)
 $640万
 $23,181/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="G23" s="24" t="inlineStr">
@@ -13141,7 +13141,7 @@
           <t>F | 288呎 (1房)
 $646万
 $22,448/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="H23" s="24" t="inlineStr">
@@ -13149,7 +13149,7 @@
           <t>G | 277呎 (1房)
 $644万
 $23,249/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="I23" s="23" t="inlineStr">
@@ -13180,7 +13180,7 @@
           <t>A | 389呎 (2房)
 $873万
 $22,450/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
@@ -13188,7 +13188,7 @@
           <t>B | 241呎 (1房)
 $576万
 $23,900/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="D24" s="24" t="inlineStr">
@@ -13196,7 +13196,7 @@
           <t>C | 438呎 (2房)
 $981万
 $22,400/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="E24" s="24" t="inlineStr">
@@ -13204,7 +13204,7 @@
           <t>D | 271呎 (1房)
 $572万
 $21,114/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="F24" s="24" t="inlineStr">
@@ -13212,7 +13212,7 @@
           <t>E | 276呎 (1房)
 $608万
 $22,040/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="G24" s="24" t="inlineStr">
@@ -13220,7 +13220,7 @@
           <t>F | 288呎 (1房)
 $665万
 $23,097/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="H24" s="24" t="inlineStr">
@@ -13228,7 +13228,7 @@
           <t>G | 277呎 (1房)
 $616万
 $22,249/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="I24" s="23" t="inlineStr">
@@ -13267,7 +13267,7 @@
           <t>B | 241呎 (1房)
 $569万
 $23,602/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -13283,15 +13283,15 @@
           <t>D | 271呎 (1房)
 $564万
 $20,812/呎
-(26年-05月-31日)</t>
-        </is>
-      </c>
-      <c r="F25" s="23" t="inlineStr">
+(26年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
         <is>
           <t>E | 276呎 (1房)
-$752万
-$27,264/呎
-(在售)</t>
+$622万
+$22,554/呎
+(26年-07月-25日)</t>
         </is>
       </c>
       <c r="G25" s="24" t="inlineStr">
@@ -13299,7 +13299,7 @@
           <t>F | 288呎 (1房)
 $662万
 $22,976/呎
-(26年-06月-17日)</t>
+(26年-06月-18日)</t>
         </is>
       </c>
       <c r="H25" s="24" t="inlineStr">
@@ -13307,7 +13307,7 @@
           <t>G | 277呎 (1房)
 $621万
 $22,422/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="I25" s="23" t="inlineStr">
@@ -13338,7 +13338,7 @@
           <t>A | 389呎 (2房)
 $884万
 $22,735/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -13346,7 +13346,7 @@
           <t>B | 241呎 (1房)
 $571万
 $23,701/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -13362,7 +13362,7 @@
           <t>D | 271呎 (1房)
 $573万
 $21,159/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="F26" s="24" t="inlineStr">
@@ -13370,7 +13370,7 @@
           <t>E | 276呎 (1房)
 $614万
 $22,243/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="G26" s="24" t="inlineStr">
@@ -13378,7 +13378,7 @@
           <t>F | 288呎 (1房)
 $631万
 $21,899/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="H26" s="24" t="inlineStr">
@@ -13386,7 +13386,7 @@
           <t>G | 277呎 (1房)
 $618万
 $22,325/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="I26" s="23" t="inlineStr">
@@ -13425,7 +13425,7 @@
           <t>B | 241呎 (1房)
 $571万
 $23,705/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
@@ -13441,7 +13441,7 @@
           <t>D | 271呎 (1房)
 $556万
 $20,506/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
@@ -13457,7 +13457,7 @@
           <t>F | 288呎 (1房)
 $624万
 $21,649/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="H27" s="24" t="inlineStr">
@@ -13465,7 +13465,7 @@
           <t>G | 277呎 (1房)
 $586万
 $21,141/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="I27" s="23" t="inlineStr">
@@ -13491,7 +13491,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 350呎 (2房)
 -
@@ -13499,7 +13499,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="21" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 204呎 (1房)
 -
@@ -13507,7 +13507,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 401呎 (2房)
 -
@@ -13515,7 +13515,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E28" s="21" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 234呎 (1房)
 -
@@ -13523,7 +13523,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F28" s="21" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>E | 238呎 (1房)
 -
@@ -13531,7 +13531,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G28" s="21" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>F | 250呎 (1房)
 -
@@ -13539,7 +13539,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H28" s="21" t="inlineStr">
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>G | 240呎 (1房)
 -
@@ -13547,7 +13547,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I28" s="21" t="inlineStr">
+      <c r="I28" s="20" t="inlineStr">
         <is>
           <t>H | 192呎 (开放式)
 -
@@ -13555,7 +13555,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J28" s="21" t="inlineStr">
+      <c r="J28" s="20" t="inlineStr">
         <is>
           <t>J | 199呎 (开放式)
 -

--- a/files/港岛-香港仔及鸭脷洲-PORTO.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-PORTO.xlsx
@@ -271,10 +271,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -11965,10 +11965,33 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr"/>
+      <c r="G5" s="20" t="inlineStr"/>
+      <c r="H5" s="20" t="inlineStr"/>
+      <c r="I5" s="20" t="inlineStr"/>
+      <c r="J5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
           <t>28&amp;29</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A | 757呎 (3房)
 -
@@ -11976,7 +11999,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 746呎 (3房)
 -
@@ -11984,8 +12007,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr"/>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>D | 644呎 (2房)
 -
@@ -11993,34 +12016,11 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr"/>
-      <c r="G5" s="21" t="inlineStr"/>
-      <c r="H5" s="21" t="inlineStr"/>
-      <c r="I5" s="21" t="inlineStr"/>
-      <c r="J5" s="21" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>C | 286呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="21" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr"/>
-      <c r="H6" s="21" t="inlineStr"/>
-      <c r="I6" s="21" t="inlineStr"/>
-      <c r="J6" s="21" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -12028,7 +12028,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 388呎 (2房)
 -
@@ -12044,7 +12044,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12068,7 +12068,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12076,7 +12076,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12084,8 +12084,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I7" s="21" t="inlineStr"/>
-      <c r="J7" s="21" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
+      <c r="J7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -12093,7 +12093,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 388呎 (2房)
 -
@@ -12109,7 +12109,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12133,7 +12133,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12141,7 +12141,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12149,8 +12149,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I8" s="21" t="inlineStr"/>
-      <c r="J8" s="21" t="inlineStr"/>
+      <c r="I8" s="20" t="inlineStr"/>
+      <c r="J8" s="20" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -12174,7 +12174,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12198,7 +12198,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G9" s="20" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12206,7 +12206,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12214,8 +12214,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I9" s="21" t="inlineStr"/>
-      <c r="J9" s="21" t="inlineStr"/>
+      <c r="I9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -12263,7 +12263,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G10" s="20" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12271,7 +12271,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12279,8 +12279,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I10" s="21" t="inlineStr"/>
-      <c r="J10" s="21" t="inlineStr"/>
+      <c r="I10" s="20" t="inlineStr"/>
+      <c r="J10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -12328,7 +12328,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G11" s="20" t="inlineStr">
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12336,7 +12336,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H11" s="20" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12344,8 +12344,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I11" s="21" t="inlineStr"/>
-      <c r="J11" s="21" t="inlineStr"/>
+      <c r="I11" s="20" t="inlineStr"/>
+      <c r="J11" s="20" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -12393,7 +12393,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G12" s="20" t="inlineStr">
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12401,7 +12401,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H12" s="20" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12409,8 +12409,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I12" s="21" t="inlineStr"/>
-      <c r="J12" s="21" t="inlineStr"/>
+      <c r="I12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr"/>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -12466,7 +12466,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H13" s="20" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12474,8 +12474,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I13" s="21" t="inlineStr"/>
-      <c r="J13" s="21" t="inlineStr"/>
+      <c r="I13" s="20" t="inlineStr"/>
+      <c r="J13" s="20" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -12531,7 +12531,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H14" s="20" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12539,8 +12539,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I14" s="21" t="inlineStr"/>
-      <c r="J14" s="21" t="inlineStr"/>
+      <c r="I14" s="20" t="inlineStr"/>
+      <c r="J14" s="20" t="inlineStr"/>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -12604,8 +12604,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I15" s="21" t="inlineStr"/>
-      <c r="J15" s="21" t="inlineStr"/>
+      <c r="I15" s="20" t="inlineStr"/>
+      <c r="J15" s="20" t="inlineStr"/>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -12669,8 +12669,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I16" s="21" t="inlineStr"/>
-      <c r="J16" s="21" t="inlineStr"/>
+      <c r="I16" s="20" t="inlineStr"/>
+      <c r="J16" s="20" t="inlineStr"/>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -12734,8 +12734,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I17" s="21" t="inlineStr"/>
-      <c r="J17" s="21" t="inlineStr"/>
+      <c r="I17" s="20" t="inlineStr"/>
+      <c r="J17" s="20" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -12799,8 +12799,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I18" s="21" t="inlineStr"/>
-      <c r="J18" s="21" t="inlineStr"/>
+      <c r="I18" s="20" t="inlineStr"/>
+      <c r="J18" s="20" t="inlineStr"/>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
@@ -12864,8 +12864,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I19" s="21" t="inlineStr"/>
-      <c r="J19" s="21" t="inlineStr"/>
+      <c r="I19" s="20" t="inlineStr"/>
+      <c r="J19" s="20" t="inlineStr"/>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
@@ -12905,7 +12905,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F20" s="20" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>E | 296呎 (1房)
 -
@@ -12913,7 +12913,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G20" s="20" t="inlineStr">
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>F | 346呎 (2房)
 -
@@ -12929,8 +12929,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I20" s="21" t="inlineStr"/>
-      <c r="J20" s="21" t="inlineStr"/>
+      <c r="I20" s="20" t="inlineStr"/>
+      <c r="J20" s="20" t="inlineStr"/>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
@@ -13491,7 +13491,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>A | 350呎 (2房)
 -
@@ -13499,7 +13499,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 204呎 (1房)
 -
@@ -13507,7 +13507,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 401呎 (2房)
 -
@@ -13515,7 +13515,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E28" s="20" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 234呎 (1房)
 -
@@ -13523,7 +13523,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F28" s="20" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 238呎 (1房)
 -
@@ -13531,7 +13531,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G28" s="20" t="inlineStr">
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>F | 250呎 (1房)
 -
@@ -13539,7 +13539,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H28" s="20" t="inlineStr">
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>G | 240呎 (1房)
 -
@@ -13547,7 +13547,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I28" s="20" t="inlineStr">
+      <c r="I28" s="21" t="inlineStr">
         <is>
           <t>H | 192呎 (开放式)
 -
@@ -13555,7 +13555,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J28" s="20" t="inlineStr">
+      <c r="J28" s="21" t="inlineStr">
         <is>
           <t>J | 199呎 (开放式)
 -

--- a/files/港岛-香港仔及鸭脷洲-PORTO.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-PORTO.xlsx
@@ -271,10 +271,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -11965,12 +11965,49 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
+          <t>28&amp;29</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 746呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 644呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+      <c r="H5" s="21" t="inlineStr"/>
+      <c r="I5" s="21" t="inlineStr"/>
+      <c r="J5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="20" t="inlineStr"/>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 286呎 (1房)
 -
@@ -11978,49 +12015,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr"/>
-      <c r="F5" s="20" t="inlineStr"/>
-      <c r="G5" s="20" t="inlineStr"/>
-      <c r="H5" s="20" t="inlineStr"/>
-      <c r="I5" s="20" t="inlineStr"/>
-      <c r="J5" s="20" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>28&amp;29</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>B | 746呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr">
-        <is>
-          <t>D | 644呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+      <c r="I6" s="21" t="inlineStr"/>
+      <c r="J6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -12028,7 +12028,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 388呎 (2房)
 -
@@ -12044,7 +12044,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12068,7 +12068,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12076,7 +12076,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12084,8 +12084,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr"/>
-      <c r="J7" s="20" t="inlineStr"/>
+      <c r="I7" s="21" t="inlineStr"/>
+      <c r="J7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -12093,7 +12093,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 388呎 (2房)
 -
@@ -12109,7 +12109,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12133,7 +12133,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12141,7 +12141,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12149,8 +12149,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I8" s="20" t="inlineStr"/>
-      <c r="J8" s="20" t="inlineStr"/>
+      <c r="I8" s="21" t="inlineStr"/>
+      <c r="J8" s="21" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -12174,7 +12174,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12198,7 +12198,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12206,7 +12206,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12214,8 +12214,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I9" s="20" t="inlineStr"/>
-      <c r="J9" s="20" t="inlineStr"/>
+      <c r="I9" s="21" t="inlineStr"/>
+      <c r="J9" s="21" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -12263,7 +12263,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12271,7 +12271,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H10" s="21" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12279,8 +12279,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I10" s="20" t="inlineStr"/>
-      <c r="J10" s="20" t="inlineStr"/>
+      <c r="I10" s="21" t="inlineStr"/>
+      <c r="J10" s="21" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -12328,7 +12328,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12336,7 +12336,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H11" s="21" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12344,8 +12344,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I11" s="20" t="inlineStr"/>
-      <c r="J11" s="20" t="inlineStr"/>
+      <c r="I11" s="21" t="inlineStr"/>
+      <c r="J11" s="21" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -12393,7 +12393,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12401,7 +12401,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12409,8 +12409,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I12" s="20" t="inlineStr"/>
-      <c r="J12" s="20" t="inlineStr"/>
+      <c r="I12" s="21" t="inlineStr"/>
+      <c r="J12" s="21" t="inlineStr"/>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -12466,7 +12466,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H13" s="21" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12474,8 +12474,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I13" s="20" t="inlineStr"/>
-      <c r="J13" s="20" t="inlineStr"/>
+      <c r="I13" s="21" t="inlineStr"/>
+      <c r="J13" s="21" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -12531,7 +12531,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H14" s="21" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12539,8 +12539,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I14" s="20" t="inlineStr"/>
-      <c r="J14" s="20" t="inlineStr"/>
+      <c r="I14" s="21" t="inlineStr"/>
+      <c r="J14" s="21" t="inlineStr"/>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -12604,8 +12604,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I15" s="20" t="inlineStr"/>
-      <c r="J15" s="20" t="inlineStr"/>
+      <c r="I15" s="21" t="inlineStr"/>
+      <c r="J15" s="21" t="inlineStr"/>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -12669,8 +12669,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I16" s="20" t="inlineStr"/>
-      <c r="J16" s="20" t="inlineStr"/>
+      <c r="I16" s="21" t="inlineStr"/>
+      <c r="J16" s="21" t="inlineStr"/>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -12734,8 +12734,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I17" s="20" t="inlineStr"/>
-      <c r="J17" s="20" t="inlineStr"/>
+      <c r="I17" s="21" t="inlineStr"/>
+      <c r="J17" s="21" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -12799,8 +12799,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I18" s="20" t="inlineStr"/>
-      <c r="J18" s="20" t="inlineStr"/>
+      <c r="I18" s="21" t="inlineStr"/>
+      <c r="J18" s="21" t="inlineStr"/>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
@@ -12864,8 +12864,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I19" s="20" t="inlineStr"/>
-      <c r="J19" s="20" t="inlineStr"/>
+      <c r="I19" s="21" t="inlineStr"/>
+      <c r="J19" s="21" t="inlineStr"/>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
@@ -12905,7 +12905,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 296呎 (1房)
 -
@@ -12913,7 +12913,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G20" s="21" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 346呎 (2房)
 -
@@ -12929,8 +12929,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I20" s="20" t="inlineStr"/>
-      <c r="J20" s="20" t="inlineStr"/>
+      <c r="I20" s="21" t="inlineStr"/>
+      <c r="J20" s="21" t="inlineStr"/>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
@@ -13491,7 +13491,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 350呎 (2房)
 -
@@ -13499,7 +13499,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="21" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 204呎 (1房)
 -
@@ -13507,7 +13507,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 401呎 (2房)
 -
@@ -13515,7 +13515,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E28" s="21" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 234呎 (1房)
 -
@@ -13523,7 +13523,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F28" s="21" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>E | 238呎 (1房)
 -
@@ -13531,7 +13531,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G28" s="21" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>F | 250呎 (1房)
 -
@@ -13539,7 +13539,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H28" s="21" t="inlineStr">
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>G | 240呎 (1房)
 -
@@ -13547,7 +13547,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I28" s="21" t="inlineStr">
+      <c r="I28" s="20" t="inlineStr">
         <is>
           <t>H | 192呎 (开放式)
 -
@@ -13555,7 +13555,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J28" s="21" t="inlineStr">
+      <c r="J28" s="20" t="inlineStr">
         <is>
           <t>J | 199呎 (开放式)
 -

--- a/files/港岛-香港仔及鸭脷洲-PORTO.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-PORTO.xlsx
@@ -271,10 +271,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -9784,7 +9784,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -11965,12 +11965,49 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
+          <t>28&amp;29</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 746呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 644呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+      <c r="H5" s="21" t="inlineStr"/>
+      <c r="I5" s="21" t="inlineStr"/>
+      <c r="J5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="20" t="inlineStr"/>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 286呎 (1房)
 -
@@ -11978,49 +12015,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr"/>
-      <c r="F5" s="20" t="inlineStr"/>
-      <c r="G5" s="20" t="inlineStr"/>
-      <c r="H5" s="20" t="inlineStr"/>
-      <c r="I5" s="20" t="inlineStr"/>
-      <c r="J5" s="20" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>28&amp;29</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>B | 746呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr">
-        <is>
-          <t>D | 644呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+      <c r="I6" s="21" t="inlineStr"/>
+      <c r="J6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -12028,7 +12028,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 388呎 (2房)
 -
@@ -12044,7 +12044,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12068,7 +12068,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12076,7 +12076,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12084,8 +12084,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr"/>
-      <c r="J7" s="20" t="inlineStr"/>
+      <c r="I7" s="21" t="inlineStr"/>
+      <c r="J7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -12093,7 +12093,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 388呎 (2房)
 -
@@ -12109,7 +12109,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12133,7 +12133,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12141,7 +12141,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12149,8 +12149,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I8" s="20" t="inlineStr"/>
-      <c r="J8" s="20" t="inlineStr"/>
+      <c r="I8" s="21" t="inlineStr"/>
+      <c r="J8" s="21" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -12174,7 +12174,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12198,7 +12198,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12206,7 +12206,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12214,8 +12214,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I9" s="20" t="inlineStr"/>
-      <c r="J9" s="20" t="inlineStr"/>
+      <c r="I9" s="21" t="inlineStr"/>
+      <c r="J9" s="21" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -12263,7 +12263,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12271,7 +12271,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H10" s="21" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12279,8 +12279,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I10" s="20" t="inlineStr"/>
-      <c r="J10" s="20" t="inlineStr"/>
+      <c r="I10" s="21" t="inlineStr"/>
+      <c r="J10" s="21" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -12328,7 +12328,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12336,7 +12336,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H11" s="21" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12344,8 +12344,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I11" s="20" t="inlineStr"/>
-      <c r="J11" s="20" t="inlineStr"/>
+      <c r="I11" s="21" t="inlineStr"/>
+      <c r="J11" s="21" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -12393,7 +12393,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12401,7 +12401,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12409,8 +12409,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I12" s="20" t="inlineStr"/>
-      <c r="J12" s="20" t="inlineStr"/>
+      <c r="I12" s="21" t="inlineStr"/>
+      <c r="J12" s="21" t="inlineStr"/>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -12466,7 +12466,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H13" s="21" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12474,8 +12474,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I13" s="20" t="inlineStr"/>
-      <c r="J13" s="20" t="inlineStr"/>
+      <c r="I13" s="21" t="inlineStr"/>
+      <c r="J13" s="21" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -12531,7 +12531,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H14" s="21" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12539,8 +12539,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I14" s="20" t="inlineStr"/>
-      <c r="J14" s="20" t="inlineStr"/>
+      <c r="I14" s="21" t="inlineStr"/>
+      <c r="J14" s="21" t="inlineStr"/>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -12604,8 +12604,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I15" s="20" t="inlineStr"/>
-      <c r="J15" s="20" t="inlineStr"/>
+      <c r="I15" s="21" t="inlineStr"/>
+      <c r="J15" s="21" t="inlineStr"/>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -12669,8 +12669,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I16" s="20" t="inlineStr"/>
-      <c r="J16" s="20" t="inlineStr"/>
+      <c r="I16" s="21" t="inlineStr"/>
+      <c r="J16" s="21" t="inlineStr"/>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -12734,8 +12734,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I17" s="20" t="inlineStr"/>
-      <c r="J17" s="20" t="inlineStr"/>
+      <c r="I17" s="21" t="inlineStr"/>
+      <c r="J17" s="21" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -12799,8 +12799,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I18" s="20" t="inlineStr"/>
-      <c r="J18" s="20" t="inlineStr"/>
+      <c r="I18" s="21" t="inlineStr"/>
+      <c r="J18" s="21" t="inlineStr"/>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
@@ -12864,8 +12864,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I19" s="20" t="inlineStr"/>
-      <c r="J19" s="20" t="inlineStr"/>
+      <c r="I19" s="21" t="inlineStr"/>
+      <c r="J19" s="21" t="inlineStr"/>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
@@ -12905,7 +12905,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 296呎 (1房)
 -
@@ -12913,7 +12913,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G20" s="21" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 346呎 (2房)
 -
@@ -12929,8 +12929,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I20" s="20" t="inlineStr"/>
-      <c r="J20" s="20" t="inlineStr"/>
+      <c r="I20" s="21" t="inlineStr"/>
+      <c r="J20" s="21" t="inlineStr"/>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
@@ -13291,7 +13291,7 @@
           <t>E | 276呎 (1房)
 $622万
 $22,554/呎
-(26年-07月-25日)</t>
+(26年-08月-14日)</t>
         </is>
       </c>
       <c r="G25" s="24" t="inlineStr">
@@ -13491,7 +13491,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 350呎 (2房)
 -
@@ -13499,7 +13499,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="21" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 204呎 (1房)
 -
@@ -13507,7 +13507,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 401呎 (2房)
 -
@@ -13515,7 +13515,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E28" s="21" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 234呎 (1房)
 -
@@ -13523,7 +13523,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F28" s="21" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>E | 238呎 (1房)
 -
@@ -13531,7 +13531,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G28" s="21" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>F | 250呎 (1房)
 -
@@ -13539,7 +13539,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H28" s="21" t="inlineStr">
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>G | 240呎 (1房)
 -
@@ -13547,7 +13547,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I28" s="21" t="inlineStr">
+      <c r="I28" s="20" t="inlineStr">
         <is>
           <t>H | 192呎 (开放式)
 -
@@ -13555,7 +13555,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J28" s="21" t="inlineStr">
+      <c r="J28" s="20" t="inlineStr">
         <is>
           <t>J | 199呎 (开放式)
 -

--- a/files/港岛-香港仔及鸭脷洲-PORTO.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-PORTO.xlsx
@@ -6358,7 +6358,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -12748,7 +12748,7 @@
           <t>A | 388呎 (2房)
 $974万
 $25,103/呎
-(26年-05月-19日)</t>
+(26年-08月-20日)</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-PORTO.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-PORTO.xlsx
@@ -271,10 +271,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N66" s="3" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr">
@@ -5078,7 +5078,7 @@
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N71" s="3" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N77" s="3" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N85" s="3" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N87" s="3" t="inlineStr">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="M91" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N91" s="3" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N92" s="3" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N94" s="3" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N98" s="3" t="inlineStr">
@@ -7078,7 +7078,7 @@
       </c>
       <c r="M101" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N101" s="3" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="M104" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N104" s="3" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="M105" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N105" s="3" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N106" s="3" t="inlineStr">
@@ -7609,34 +7609,34 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
-        <v>7483000</v>
+        <v>6248000</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>27613</v>
+        <v>23055</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K110" s="5" t="n">
-        <v>6248305</v>
+        <v>6248000</v>
       </c>
       <c r="L110" s="5" t="n">
-        <v>23056</v>
+        <v>23055</v>
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N110" s="3" t="inlineStr">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="M111" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N111" s="3" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="M114" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N114" s="3" t="inlineStr">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="M115" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N115" s="3" t="inlineStr">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="M123" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N123" s="3" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="M124" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N124" s="3" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="M129" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N129" s="3" t="inlineStr">
@@ -9000,7 +9000,7 @@
       </c>
       <c r="M132" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N132" s="3" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="M133" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N133" s="3" t="inlineStr">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="M141" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N141" s="3" t="inlineStr">
@@ -9620,7 +9620,7 @@
       </c>
       <c r="M142" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N142" s="3" t="inlineStr">
@@ -9930,7 +9930,7 @@
       </c>
       <c r="M147" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N147" s="3" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="M149" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N149" s="3" t="inlineStr">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="M150" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N150" s="3" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="M151" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N151" s="3" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="M156" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N156" s="3" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="M159" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N159" s="3" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="M160" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N160" s="3" t="inlineStr">
@@ -10922,7 +10922,7 @@
       </c>
       <c r="M163" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N163" s="3" t="inlineStr">
@@ -11046,7 +11046,7 @@
       </c>
       <c r="M165" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N165" s="3" t="inlineStr">
@@ -11170,7 +11170,7 @@
       </c>
       <c r="M167" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N167" s="3" t="inlineStr">
@@ -11886,7 +11886,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>66</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -11965,10 +11965,33 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr"/>
+      <c r="G5" s="20" t="inlineStr"/>
+      <c r="H5" s="20" t="inlineStr"/>
+      <c r="I5" s="20" t="inlineStr"/>
+      <c r="J5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
           <t>28&amp;29</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A | 757呎 (3房)
 -
@@ -11976,7 +11999,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 746呎 (3房)
 -
@@ -11984,8 +12007,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr"/>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>D | 644呎 (2房)
 -
@@ -11993,34 +12016,11 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr"/>
-      <c r="G5" s="21" t="inlineStr"/>
-      <c r="H5" s="21" t="inlineStr"/>
-      <c r="I5" s="21" t="inlineStr"/>
-      <c r="J5" s="21" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>C | 286呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="21" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr"/>
-      <c r="H6" s="21" t="inlineStr"/>
-      <c r="I6" s="21" t="inlineStr"/>
-      <c r="J6" s="21" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -12028,7 +12028,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 388呎 (2房)
 -
@@ -12044,7 +12044,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12068,7 +12068,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12076,7 +12076,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12084,8 +12084,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I7" s="21" t="inlineStr"/>
-      <c r="J7" s="21" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
+      <c r="J7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -12093,7 +12093,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 388呎 (2房)
 -
@@ -12109,7 +12109,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12133,7 +12133,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12141,7 +12141,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12149,8 +12149,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I8" s="21" t="inlineStr"/>
-      <c r="J8" s="21" t="inlineStr"/>
+      <c r="I8" s="20" t="inlineStr"/>
+      <c r="J8" s="20" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -12174,7 +12174,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12198,7 +12198,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G9" s="20" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12206,7 +12206,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12214,8 +12214,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I9" s="21" t="inlineStr"/>
-      <c r="J9" s="21" t="inlineStr"/>
+      <c r="I9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -12263,7 +12263,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G10" s="20" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12271,7 +12271,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12279,8 +12279,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I10" s="21" t="inlineStr"/>
-      <c r="J10" s="21" t="inlineStr"/>
+      <c r="I10" s="20" t="inlineStr"/>
+      <c r="J10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -12328,7 +12328,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G11" s="20" t="inlineStr">
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12336,7 +12336,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H11" s="20" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12344,8 +12344,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I11" s="21" t="inlineStr"/>
-      <c r="J11" s="21" t="inlineStr"/>
+      <c r="I11" s="20" t="inlineStr"/>
+      <c r="J11" s="20" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -12393,7 +12393,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G12" s="20" t="inlineStr">
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12401,7 +12401,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H12" s="20" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12409,8 +12409,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I12" s="21" t="inlineStr"/>
-      <c r="J12" s="21" t="inlineStr"/>
+      <c r="I12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr"/>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -12466,7 +12466,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H13" s="20" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12474,8 +12474,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I13" s="21" t="inlineStr"/>
-      <c r="J13" s="21" t="inlineStr"/>
+      <c r="I13" s="20" t="inlineStr"/>
+      <c r="J13" s="20" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -12531,7 +12531,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H14" s="20" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12539,8 +12539,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I14" s="21" t="inlineStr"/>
-      <c r="J14" s="21" t="inlineStr"/>
+      <c r="I14" s="20" t="inlineStr"/>
+      <c r="J14" s="20" t="inlineStr"/>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -12604,8 +12604,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I15" s="21" t="inlineStr"/>
-      <c r="J15" s="21" t="inlineStr"/>
+      <c r="I15" s="20" t="inlineStr"/>
+      <c r="J15" s="20" t="inlineStr"/>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -12669,8 +12669,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I16" s="21" t="inlineStr"/>
-      <c r="J16" s="21" t="inlineStr"/>
+      <c r="I16" s="20" t="inlineStr"/>
+      <c r="J16" s="20" t="inlineStr"/>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -12734,8 +12734,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I17" s="21" t="inlineStr"/>
-      <c r="J17" s="21" t="inlineStr"/>
+      <c r="I17" s="20" t="inlineStr"/>
+      <c r="J17" s="20" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -12799,8 +12799,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I18" s="21" t="inlineStr"/>
-      <c r="J18" s="21" t="inlineStr"/>
+      <c r="I18" s="20" t="inlineStr"/>
+      <c r="J18" s="20" t="inlineStr"/>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
@@ -12864,8 +12864,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I19" s="21" t="inlineStr"/>
-      <c r="J19" s="21" t="inlineStr"/>
+      <c r="I19" s="20" t="inlineStr"/>
+      <c r="J19" s="20" t="inlineStr"/>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
@@ -12905,7 +12905,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F20" s="20" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>E | 296呎 (1房)
 -
@@ -12913,7 +12913,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G20" s="20" t="inlineStr">
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>F | 346呎 (2房)
 -
@@ -12929,8 +12929,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I20" s="21" t="inlineStr"/>
-      <c r="J20" s="21" t="inlineStr"/>
+      <c r="I20" s="20" t="inlineStr"/>
+      <c r="J20" s="20" t="inlineStr"/>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
@@ -12962,12 +12962,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E21" s="24" t="inlineStr">
         <is>
           <t>D | 271呎 (1房)
-$748万
-$27,613/呎
-(在售)</t>
+$625万
+$23,055/呎
+(26年-09月-02日)</t>
         </is>
       </c>
       <c r="F21" s="24" t="inlineStr">
@@ -13491,7 +13491,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>A | 350呎 (2房)
 -
@@ -13499,7 +13499,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 204呎 (1房)
 -
@@ -13507,7 +13507,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 401呎 (2房)
 -
@@ -13515,7 +13515,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E28" s="20" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 234呎 (1房)
 -
@@ -13523,7 +13523,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F28" s="20" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 238呎 (1房)
 -
@@ -13531,7 +13531,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G28" s="20" t="inlineStr">
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>F | 250呎 (1房)
 -
@@ -13539,7 +13539,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H28" s="20" t="inlineStr">
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>G | 240呎 (1房)
 -
@@ -13547,7 +13547,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I28" s="20" t="inlineStr">
+      <c r="I28" s="21" t="inlineStr">
         <is>
           <t>H | 192呎 (开放式)
 -
@@ -13555,7 +13555,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J28" s="20" t="inlineStr">
+      <c r="J28" s="21" t="inlineStr">
         <is>
           <t>J | 199呎 (开放式)
 -
